--- a/basedatos_partidas/salida/descompuestos/12.12.01.050.xlsx
+++ b/basedatos_partidas/salida/descompuestos/12.12.01.050.xlsx
@@ -584,10 +584,10 @@
         <v>0.12</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="14">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="H22" t="n">
         <v>0.05</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
   </sheetData>
